--- a/test-cases/InternSafar-Test-Cases-2026-10-09.xlsx
+++ b/test-cases/InternSafar-Test-Cases-2026-10-09.xlsx
@@ -606,7 +606,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Candidate: lawsonlclintern+qa1@gmail.com / Admin@123 | Employer: placementhubsupport+qa1@gmail.com / Admin@123 | SuperAdmin: support@placementhub.online / Admin@123 (all on `/`)</t>
+          <t>Candidate: lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; | Employer: placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; | SuperAdmin: support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt; (all on `/`)</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -1807,7 +1807,7 @@
           <t>Legacy ID: CAND-AP-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Applications list: tableKey candidate.applications.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
@@ -1826,7 +1826,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -1912,7 +1912,7 @@
           <t>Legacy ID: CAND-AP-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Application detail sheet/dialog a11y on /candidate/applications.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
@@ -1931,7 +1931,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -2017,7 +2017,7 @@
           <t>Legacy ID: CAND-D-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -2680,7 +2680,7 @@
           <t>Legacy ID: EMP-PL-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PATCH /api/ip/employer/applications/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -2786,7 +2786,7 @@
           <t>Legacy ID: EMP-PL-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: applications/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -2889,7 +2889,7 @@
           <t>Legacy ID: EMP-PL-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/offers POST
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -2991,7 +2991,7 @@
           <t>Legacy ID: EMP-PL-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offers POST ownership check
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -3094,7 +3094,7 @@
           <t>Legacy ID: EMP-PL-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/completions
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -3196,7 +3196,7 @@
           <t>Legacy ID: EMP-AN-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer/analytics
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -3298,7 +3298,7 @@
           <t>Legacy ID: EMP-PL-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: employer/applications/[id] ALLOWED
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -3400,7 +3400,7 @@
           <t>Legacy ID: EMP-PL-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: parseInterviewMeetUrl
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123 posting with applicants</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; posting with applicants</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123; searchable candidate from search or applicant</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; searchable candidate from search or applicant</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -5435,7 +5435,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -5643,7 +5643,7 @@
           <t>Legacy ID: CAND-O-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PATCH /api/ip/offers/[id] status=accepted
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -5745,7 +5745,7 @@
           <t>Legacy ID: CAND-O-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PATCH offers/[id] declined
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -5848,7 +5848,7 @@
           <t>Legacy ID: CAND-O-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offerIsExpired + status pending check
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -5950,7 +5950,7 @@
           <t>Legacy ID: CAND-O-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offers/[id] requireSession(['candidate'])
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -6053,7 +6053,7 @@
           <t>Legacy ID: CAND-O-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate/offers
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -6155,7 +6155,7 @@
           <t>Legacy ID: CAND-O-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offers/[id] PATCH
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -6257,7 +6257,7 @@
           <t>Legacy ID: CAND-O-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offers/[id] candidate_id match
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -6360,7 +6360,7 @@
           <t>Legacy ID: OFF-R-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offers/[id]/remind</t>
         </is>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -6461,7 +6461,7 @@
           <t>Legacy ID: COMP-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: completions ownership</t>
         </is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -6562,7 +6562,7 @@
           <t>Legacy ID: COMP-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: completions</t>
         </is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -6665,7 +6665,7 @@
           <t>Legacy ID: RATE-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/ratings /api/ip/endorsements</t>
         </is>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -6766,7 +6766,7 @@
           <t>Legacy ID: RATE-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/ratings</t>
         </is>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>EP: missing both applicationId and candidate+internship vs candidate+internship with no apply vs valid applicationId. Risk 3×3=9 (orphan offers). Trace: migrations 019/023. Demo: placementhubsupport+qa1@gmail.com / Admin@123 / lawsonlclintern+2@gmail.com / Admin@123 if +2 has not applied to that posting.</t>
+          <t>EP: missing both applicationId and candidate+internship vs candidate+internship with no apply vs valid applicationId. Risk 3×3=9 (orphan offers). Trace: migrations 019/023. Demo: placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; / lawsonlclintern+2@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; if +2 has not applied to that posting.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123; a published internship; candidate who has not applied</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; a published internship; candidate who has not applied</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123 with an application that already has an offer, or create one then POST again</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; with an application that already has an offer, or create one then POST again</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123; lawsonlclintern+qa1@gmail.com / Admin@123 with only applied/shortlisted if possible Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; with only applied/shortlisted if possible Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -7969,7 +7969,7 @@
           <t>Legacy ID: CAND-M-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate/messages /api/ip/messages/threads
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -8072,7 +8072,7 @@
           <t>Legacy ID: CAND-M-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: threads/[id] PATCH
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -8176,7 +8176,7 @@
           <t>Legacy ID: CAND-N-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Notifications page: /candidate/notifications.
 Product reference: /candidate/notifications /api/ip/nav-badges
@@ -8194,7 +8194,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -8280,7 +8280,7 @@
           <t>Legacy ID: CAND-N-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate/notifications
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -8382,7 +8382,7 @@
           <t>Legacy ID: CAND-M-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: messages/threads POST
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -8484,7 +8484,7 @@
           <t>Legacy ID: CAND-M-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: threads/[id] POST
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -8586,7 +8586,7 @@
           <t>Legacy ID: CAND-M-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: threads/[id] membership check
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123; a notification whose meta.internshipId or offerId no longer exists (or generate one then delete the entity in a throwaway run) Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; a notification whose meta.internshipId or offerId no longer exists (or generate one then delete the entity in a throwaway run) Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123 invite vs apply paths</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; invite vs apply paths</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -9312,7 +9312,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -9520,7 +9520,7 @@
           <t>Legacy ID: CAND-R-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate/referral
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -9622,7 +9622,7 @@
           <t>Legacy ID: PTS-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: pointsEconomy.js + ip_points_ledger</t>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -9729,7 +9729,7 @@
           <t>Legacy ID: PTS-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: POST /api/ip/points/convert returns 410; no convert UI.
 Product reference: /api/ip/points/convert</t>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -10183,7 +10183,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -10390,7 +10390,7 @@
           <t>Legacy ID: SA-D-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -10499,7 +10499,7 @@
           <t>Legacy ID: SA-A-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PATCH /api/ip/superadmin/employers/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -10608,7 +10608,7 @@
           <t>Legacy ID: SA-A-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: employers/[id] ALLOWED statuses
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -10714,7 +10714,7 @@
           <t>Legacy ID: SA-A-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: superadmin/employers/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -10822,7 +10822,7 @@
           <t>Legacy ID: SA-DOC-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin/documents
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -10929,7 +10929,7 @@
           <t>Legacy ID: SA-PO-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin/postings
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -11132,7 +11132,7 @@
           <t>Legacy ID: SA-L-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin/login-report GET /api/ip/superadmin/login-report
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -11235,7 +11235,7 @@
           <t>Legacy ID: SA-L-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin/login-report
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -11338,7 +11338,7 @@
           <t>Legacy ID: SA-M-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin/messages
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -11442,7 +11442,7 @@
           <t>Legacy ID: SA-I-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /superadmin/feature-ideas
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -11544,7 +11544,7 @@
           <t>Legacy ID: SA-E-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/superadmin/export-audit
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -11646,7 +11646,7 @@
           <t>Legacy ID: SA-A-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: superadmin/employers/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
@@ -13119,7 +13119,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -13327,7 +13327,7 @@
           <t>Legacy ID: IDEA-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: POST /api/ip/ideas</t>
         </is>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -13431,7 +13431,7 @@
           <t>Legacy ID: IDEA-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/ideas/[id]/vote follow comments</t>
         </is>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -13533,7 +13533,7 @@
           <t>Legacy ID: IDEA-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /ideas</t>
         </is>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -13634,7 +13634,7 @@
           <t>Legacy ID: IDEA-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: ideas POST</t>
         </is>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -13735,7 +13735,7 @@
           <t>Legacy ID: IDEA-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: ideas POST</t>
         </is>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -14091,7 +14091,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>placementhubsupport+qa1@gmail.com / Admin@123 with a Core Showcase posting that has applicants</t>
+          <t>placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; with a Core Showcase posting that has applicants</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -15117,7 +15117,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -15325,7 +15325,7 @@
           <t>Legacy ID: FILE-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Files go through /api/ip/files.
 Product reference: /api/ip/files /api/ip/candidate/profile/photo/upload</t>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -15427,7 +15427,7 @@
           <t>Legacy ID: FILE-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/files</t>
         </is>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -15528,7 +15528,7 @@
           <t>Legacy ID: FILE-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: employer/profile/logo/upload</t>
         </is>
@@ -15544,7 +15544,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -16255,7 +16255,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -16985,7 +16985,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -17193,7 +17193,7 @@
           <t>Legacy ID: EMP-P-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer/profile
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -17302,7 +17302,7 @@
           <t>Legacy ID: EMP-P-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/employer/documents
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -17411,7 +17411,7 @@
           <t>Legacy ID: EMP-P-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: employerEthics + profile PUT
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17432,7 +17432,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -17518,7 +17518,7 @@
           <t>Legacy ID: EMP-H-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -17627,7 +17627,7 @@
           <t>Legacy ID: EMP-I-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: POST /api/ip/employer/internships
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17644,7 +17644,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -17730,7 +17730,7 @@
           <t>Legacy ID: EMP-I-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Publish costs 50 points; draft does not.
 Publish DT: points&gt;=50 × approved × profile_complete × not already published.
@@ -17749,7 +17749,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -17835,7 +17835,7 @@
           <t>Legacy ID: EMP-I-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships POST
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -17937,7 +17937,7 @@
           <t>Legacy ID: EMP-I-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships POST approval_status
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -18039,7 +18039,7 @@
           <t>Legacy ID: EMP-I-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships POST profileGate
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18056,7 +18056,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -18141,7 +18141,7 @@
           <t>Legacy ID: EMP-I-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships POST
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -18244,7 +18244,7 @@
           <t>Legacy ID: EMP-I-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PUT/DELETE /api/ip/employer/internships/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -18348,7 +18348,7 @@
           <t>Legacy ID: EMP-I-8 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer/internships/new  [id]/edit
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18365,7 +18365,7 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -18450,7 +18450,7 @@
           <t>Legacy ID: EMP-I-9 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships/[id] loadOwned
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18467,7 +18467,7 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -18555,7 +18555,7 @@
           <t>Legacy ID: EMP-C-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Full-page profile at /employer/candidates/[id] (not a modal).
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
@@ -18574,7 +18574,7 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
@@ -18661,7 +18661,7 @@
           <t>Legacy ID: EMP-C-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Search filters + invite from full-page profile or search row.
 Product reference: /employer/candidates
@@ -18679,7 +18679,7 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -18766,7 +18766,7 @@
           <t>Legacy ID: EMP-M-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer/messages
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
@@ -18869,7 +18869,7 @@
           <t>Legacy ID: EMP-O-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer/offers
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18886,7 +18886,7 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
@@ -18973,7 +18973,7 @@
           <t>Legacy ID: EMP-R-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /employer/referral
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -18994,7 +18994,7 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
@@ -19081,7 +19081,7 @@
           <t>Legacy ID: EMP-N-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Employer notifications: /employer/notifications.
 Product reference: /employer/notifications
@@ -19099,7 +19099,7 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
@@ -19186,7 +19186,7 @@
           <t>Legacy ID: EMP-I-10 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships/[id] PUT existing.status !== published
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
@@ -19289,7 +19289,7 @@
           <t>Legacy ID: EMP-I-11 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: internships/[id] PUT republish
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
@@ -19391,7 +19391,7 @@
           <t>Legacy ID: EMP-C-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Invite requires internshipId.
 Product reference: candidates/[id]/invite
@@ -19409,7 +19409,7 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
@@ -19494,7 +19494,7 @@
           <t>Legacy ID: EMP-C-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Cannot invite on another employer’s posting.
 Product reference: invite ownership
@@ -19512,7 +19512,7 @@
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
@@ -19598,7 +19598,7 @@
           <t>Legacy ID: ERR-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: jsonError Invalid JSON</t>
         </is>
@@ -19614,7 +19614,7 @@
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
@@ -19699,7 +19699,7 @@
           <t>Legacy ID: ERR-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: offers POST optionalDate</t>
         </is>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
@@ -19804,7 +19804,7 @@
           <t>Legacy ID: MAIL-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 Product reference: README mail table + sendMail</t>
@@ -19825,7 +19825,7 @@
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>Legacy ID: SHELL-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Only candidate and employer have a Notifications nav item.
 Product reference: PortalShell + ipNav.js</t>
@@ -19934,7 +19934,7 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
@@ -20019,7 +20019,7 @@
           <t>Legacy ID: SHELL-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PortalShell signOut</t>
         </is>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
@@ -20223,7 +20223,7 @@
           <t>Legacy ID: REGX-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: README Key decisions</t>
         </is>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
@@ -20327,7 +20327,7 @@
           <t>Legacy ID: REGX-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP captcha: correct, blank, wrong, stale token, missing token.
@@ -20350,7 +20350,7 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
@@ -20437,7 +20437,7 @@
           <t>Legacy ID: NAV-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/nav-badges PortalShell fetch</t>
         </is>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
@@ -20540,7 +20540,7 @@
           <t>Legacy ID: BOOT-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+1@gmail.com / Admin@123; Employer placementhubsupport@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Bootstrap keeps placementhubsupport@gmail.com and Gmail+ showcase cores.
 Product reference: ensureIpBootstrap.js README</t>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+1@gmail.com / Admin@123. Employer placementhubsupport@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha).</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha).</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
@@ -20646,7 +20646,7 @@
           <t>Legacy ID: ERR-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: apiAuth.requireSession</t>
         </is>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S36" s="6" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
@@ -22559,7 +22559,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -22767,7 +22767,7 @@
           <t>Legacy ID: PUB-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Home sign-in uses #email and #password.
 Product reference: /  (IpSignInLanding)
@@ -22789,7 +22789,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -22877,7 +22877,7 @@
           <t>Legacy ID: PUB-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: /login redirects to `/` and keeps query params.
 Product reference: /login → /
@@ -22895,7 +22895,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -22982,7 +22982,7 @@
           <t>Legacy ID: PUB-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP captcha: correct, blank, wrong, stale token, missing token.
 Product reference: /
@@ -23000,7 +23000,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -23087,7 +23087,7 @@
           <t>Legacy ID: PUB-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /how-it-works /guidelines /help
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -23195,7 +23195,7 @@
           <t>Legacy ID: PUB-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /register
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -23212,7 +23212,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -23299,7 +23299,7 @@
           <t>Legacy ID: PUB-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /r/[code]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -23403,7 +23403,7 @@
           <t>Legacy ID: PUB-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /app
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -23420,7 +23420,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -23505,7 +23505,7 @@
           <t>Legacy ID: HELP-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /guidelines</t>
         </is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -23608,7 +23608,7 @@
           <t>Legacy ID: PUB-8 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /register*
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -23629,7 +23629,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -23872,7 +23872,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -24041,9 +24041,9 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>1. Open `/`.
-2. Candidate: lawsonlclintern+qa1@gmail.com / Admin@123 + captcha → Sign in.
-3. Sign out. Repeat as employer placementhubsupport+qa1@gmail.com / Admin@123.
-4. Sign out. Repeat as SuperAdmin support@placementhub.online / Admin@123 on the same form.</t>
+2. Candidate: lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; + captcha → Sign in.
+3. Sign out. Repeat as employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;.
+4. Sign out. Repeat as SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt; on the same form.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -24081,7 +24081,7 @@
           <t>Legacy ID: AUTH-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Candidate/employer: Gmail+ cores on `/` with captcha.
 EP captcha: correct, blank, wrong, stale token, missing token.
@@ -24104,7 +24104,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -24190,7 +24190,7 @@
           <t>Legacy ID: AUTH-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
@@ -24209,7 +24209,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -24294,7 +24294,7 @@
           <t>Legacy ID: AUTH-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
@@ -24313,7 +24313,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -24400,7 +24400,7 @@
           <t>Legacy ID: AUTH-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: auth.js SESSION_SHORT_SEC / SESSION_LONG_SEC
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -24502,7 +24502,7 @@
           <t>Legacy ID: AUTH-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: auth.js
@@ -24520,7 +24520,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -24609,7 +24609,7 @@
           <t>Legacy ID: AUTH-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: auth.js employer approval_status + email_verified_at
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -24716,7 +24716,7 @@
           <t>Legacy ID: AUTH-8 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: auth.js queryWithRetry
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -24733,7 +24733,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -24821,7 +24821,7 @@
           <t>Legacy ID: AUTH-9 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: /forgot-password POST /api/ip/auth/password-reset/request
@@ -24839,7 +24839,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -24925,7 +24925,7 @@
           <t>Legacy ID: AUTH-10 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 EP captcha: correct, blank, wrong, stale token, missing token.
@@ -24944,7 +24944,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -25032,7 +25032,7 @@
           <t>Legacy ID: AUTH-11 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 Product reference: POST /api/ip/auth/password-reset/confirm
@@ -25050,7 +25050,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -25139,7 +25139,7 @@
           <t>Legacy ID: AUTH-12 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: /account POST /api/ip/account/2fa  auth.js 2FA branch
@@ -25157,7 +25157,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -25244,7 +25244,7 @@
           <t>Legacy ID: AUTH-13 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: ipTwoFactor + auth.js
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -25347,7 +25347,7 @@
           <t>Legacy ID: AUTH-14 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: /api/ip/account/2fa actions start-disable / confirm-disable
@@ -25365,7 +25365,7 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -25414,7 +25414,7 @@
         <is>
           <t>1. Signed out, open /superadmin/login.
 2. Observe the URL.
-3. On `/` sign in with support@placementhub.online / Admin@123 + captcha.
+3. On `/` sign in with support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt; + captcha.
 4. Confirm landing page and SuperAdmin nav.</t>
         </is>
       </c>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
@@ -25556,7 +25556,7 @@
           <t>Legacy ID: AUTH-16 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /account GET/DELETE /api/ip/account/sessions
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -25573,7 +25573,7 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -25622,8 +25622,8 @@
         <is>
           <t>1. Sign in as candidate on `/` (#email/#password).
 2. Open /account.
-3. Current password Admin@123. New password must be ≥8 and include uppercase, a digit, and a special character (e.g. Admin@124).
-4. Sign in again with the new password, then restore Admin@123 if this is a shared core account.</t>
+3. Current password &lt;IP_QA_CORE_PASSWORD&gt;. New password must be ≥8 and include uppercase, a digit, and a special character (e.g. Admin@124).
+4. Sign in again with the new password, then restore &lt;IP_QA_CORE_PASSWORD&gt; if this is a shared core account.</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -25661,7 +25661,7 @@
           <t>Legacy ID: AUTH-17 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Account password change requires upper + digit + special.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
@@ -25680,7 +25680,7 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
@@ -25767,7 +25767,7 @@
           <t>Legacy ID: AUTH-18 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Weak new password on /account is rejected.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
@@ -25786,7 +25786,7 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
@@ -25871,7 +25871,7 @@
           <t>Legacy ID: AUTH-19 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/account/2fa
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -25888,7 +25888,7 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
@@ -25973,7 +25973,7 @@
           <t>Legacy ID: AUTH-20 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/account/2fa
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -25990,7 +25990,7 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
@@ -26076,7 +26076,7 @@
           <t>Legacy ID: AUTH-21 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
@@ -26096,7 +26096,7 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
@@ -26183,7 +26183,7 @@
           <t>Legacy ID: AUTH-22 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: recordLoginEvent + login-report
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -26204,7 +26204,7 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
@@ -26292,7 +26292,7 @@
           <t>Legacy ID: AUTH-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Captcha must be solved on home login.
 EP captcha: correct, blank, wrong, stale token, missing token.
@@ -26311,7 +26311,7 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
@@ -27208,7 +27208,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -27418,7 +27418,7 @@
           <t>Legacy ID: REG-C-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Gmail path emails temp password; sign in on `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
@@ -27444,7 +27444,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -27530,7 +27530,7 @@
           <t>Legacy ID: REG-C-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: authRegisterRules.isGmailAddress
@@ -27553,7 +27553,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -27638,7 +27638,7 @@
           <t>Legacy ID: REG-C-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate
@@ -27661,7 +27661,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -27748,7 +27748,7 @@
           <t>Legacy ID: REG-C-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: /register/candidate
@@ -27767,7 +27767,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -27855,7 +27855,7 @@
           <t>Legacy ID: REG-C-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate + pointsEconomy.REFERRAL_POINTS=25
@@ -27875,7 +27875,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -27959,7 +27959,7 @@
           <t>Legacy ID: REG-E-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: POST /api/ip/auth/register-employer  approval_status=pending
@@ -27983,7 +27983,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="n"/>
@@ -28061,7 +28061,7 @@
           <t>Legacy ID: REG-E-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-employer domainsMatch
@@ -28084,7 +28084,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -28169,7 +28169,7 @@
           <t>Legacy ID: REG-E-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: register-employer
 Excluded from automated QA — manual registration/account-creation testing only.
@@ -28193,7 +28193,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -28379,7 +28379,7 @@
           <t>Legacy ID: REG-E-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-employer
@@ -28402,7 +28402,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -28487,7 +28487,7 @@
           <t>Legacy ID: REG-C-8 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: authRegisterRules GMAIL_DOMAINS
@@ -28506,7 +28506,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -28592,7 +28592,7 @@
           <t>Legacy ID: REG-C-9 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate self_referral
@@ -28611,7 +28611,7 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -28696,7 +28696,7 @@
           <t>Legacy ID: REG-C-10 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: register-candidate
@@ -28715,7 +28715,7 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -29012,7 +29012,7 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
@@ -29879,7 +29879,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -30085,7 +30085,7 @@
           <t>Legacy ID: PERM-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PortalShell unauthenticated → loginHref
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30102,7 +30102,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -30189,7 +30189,7 @@
           <t>Legacy ID: PERM-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: PortalShell + role layouts
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -30297,7 +30297,7 @@
           <t>Legacy ID: PERM-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: requireSession(['candidate'])
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30314,7 +30314,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -30400,7 +30400,7 @@
           <t>Legacy ID: PERM-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: requireSession(['employer'])
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -30503,7 +30503,7 @@
           <t>Legacy ID: PERM-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: requireSession(['superadmin'])
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30520,7 +30520,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -30606,7 +30606,7 @@
           <t>Legacy ID: PERM-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /ideas ideas/layout.js
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30623,7 +30623,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -30708,7 +30708,7 @@
           <t>Legacy ID: PERM-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: requireSession(['employer'])
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30725,7 +30725,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -30810,7 +30810,7 @@
           <t>Legacy ID: PERM-8 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: requireSession(['candidate'])
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -30913,7 +30913,7 @@
           <t>Legacy ID: PERM-9 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: superadmin/layout.js pathname exception
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -30934,7 +30934,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -31177,7 +31177,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -31385,7 +31385,7 @@
           <t>Legacy ID: ACCT-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 BVA password: form register min 8; change-password min 8 + 1 upper + 1 digit + 1 special. Cases: 7, 8, 9 chars; missing class.
 Product reference: /account /api/ip/account/*</t>
@@ -31402,7 +31402,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -31488,7 +31488,7 @@
           <t>Legacy ID: ACCT-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /account</t>
         </is>
@@ -31504,7 +31504,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -31590,7 +31590,7 @@
           <t>Legacy ID: ACCT-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 EP emails: user@gmail.com (valid), user@googlemail.com (accepted), user@yahoo.com (reject), user@gmail.com.evil (reject), empty, no @.
 Product reference: notification-preferences + ipNotificationPreferences</t>
@@ -31607,7 +31607,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -31693,7 +31693,7 @@
           <t>Legacy ID: ACCT-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/account/phone-change/*</t>
         </is>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -32148,7 +32148,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -32373,7 +32373,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -32461,7 +32461,7 @@
           <t>Legacy ID: CAND-P-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Photo/privacy on tab 4; academics via /api/ip/candidate/academics.
 Product reference: candidate/profile EDITABLE_FIELDS
@@ -32483,7 +32483,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -32569,7 +32569,7 @@
           <t>Legacy ID: CAND-P-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Incomplete-profile banner on /candidate and /candidate/profile.
 Product reference: ProfileReminderBanner + /api/ip/profile-reminder
@@ -32587,7 +32587,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -32673,7 +32673,7 @@
           <t>Legacy ID: CAND-X-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Export: GET /api/ip/candidate/export from profile.
 Product reference: /api/ip/candidate/export
@@ -32695,7 +32695,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -32781,7 +32781,7 @@
           <t>Legacy ID: ACA-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Academic rows save through the academics API.
 Product reference: /api/ip/candidate/academics</t>
@@ -32798,7 +32798,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123; QA mail override if used Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; QA mail override if used Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="n"/>
@@ -33805,7 +33805,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -34012,7 +34012,7 @@
           <t>Legacy ID: CAND-B-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate/internships
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -34029,7 +34029,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S3" s="6" t="inlineStr">
@@ -34116,7 +34116,7 @@
           <t>Legacy ID: CAND-B-2 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Browse filters include minMatch, minValidation, browse tabs; tableKey candidate.internships.
 Product reference: GET /api/ip/candidate/internships
@@ -34138,7 +34138,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -34225,7 +34225,7 @@
           <t>Legacy ID: CAND-B-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Corrected/rewritten.
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Correction vs old checklist: Cards/List toggle, Filters panel, Saved views bar; mobile layout.
 Product reference: /candidate/internships
@@ -34247,7 +34247,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
@@ -34334,7 +34334,7 @@
           <t>Legacy ID: CAND-B-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /api/ip/candidate/saved
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -34351,7 +34351,7 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -34436,7 +34436,7 @@
           <t>Legacy ID: CAND-B-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: /candidate/internships/[id]
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -34540,7 +34540,7 @@
           <t>Legacy ID: CAND-A-1 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: POST /api/ip/candidate/applications POINTS_PER_APPLICATION=5
@@ -34558,7 +34558,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -34655,7 +34655,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -34740,7 +34740,7 @@
           <t>Legacy ID: CAND-A-3 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: applications POST
@@ -34758,7 +34758,7 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S10" s="6" t="inlineStr">
@@ -34844,7 +34844,7 @@
           <t>Legacy ID: CAND-A-4 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: applications screening
@@ -34862,7 +34862,7 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
@@ -34948,7 +34948,7 @@
           <t>Legacy ID: CAND-A-5 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: POINTS_PER_APPLICATION
@@ -34966,7 +34966,7 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -35149,7 +35149,7 @@
           <t>Legacy ID: CAND-A-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: applications POST
@@ -35167,7 +35167,7 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -35252,7 +35252,7 @@
           <t>Legacy ID: CAND-A-8 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Economy DT: apply costs 5 points; allowance display must not be confused with spend. EP balance 0, 4, 5, 6.
 Product reference: applications POST
@@ -35270,7 +35270,7 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -35356,7 +35356,7 @@
           <t>Legacy ID: CAND-B-6 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: candidate/internships matchesLocation
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -35373,7 +35373,7 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
@@ -35459,7 +35459,7 @@
           <t>Legacy ID: CAND-B-7 (plain text map only; Reference B is not a runtime dependency).
 Reconciliation: Carried forward (rewritten into new schema).
 QASkills test-plan: EP + BVA + decision table + risk (L×I). Status reset: Not Run.
-Seed: Candidate lawsonlclintern+qa1@gmail.com / Admin@123; Employer placementhubsupport+qa1@gmail.com / Admin@123; SA support@placementhub.online / Admin@123. No real PII; Gmail+ aliases are product demo identities.
+Seed: Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;; SA support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. No real PII; Gmail+ aliases are product demo identities.
 InternSafar logins: candidate/employer on `/` (#email, #password); SuperAdmin also on `/` (#email, #password); /superadmin/login only redirects to `/`.
 Product reference: matchesWorkMode
 Legacy ID retained for history; Playwright apply uses TC-IS-* only.</t>
@@ -35476,7 +35476,7 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / Admin@123. Employer placementhubsupport+qa1@gmail.com / Admin@123. SuperAdmin support@placementhub.online / Admin@123. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>InternSafar running (sibling internship-portal, npm run dev). Candidate lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. Employer placementhubsupport+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt;. SuperAdmin support@placementhub.online / &lt;IP_QA_SUPERADMIN_PASSWORD&gt;. All roles sign in on `/` (#email / #password + captcha). Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -35573,7 +35573,7 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
@@ -35671,7 +35671,7 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
@@ -35864,7 +35864,7 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>lawsonlclintern+qa1@gmail.com / Admin@123 Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
+          <t>lawsonlclintern+qa1@gmail.com / &lt;IP_QA_CORE_PASSWORD&gt; Test accounts only (never the core demo accounts); run `npm run qa:ensure-test-accounts` first if they are missing.</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
